--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -417,7 +417,7 @@
         <v>-23.86831275720165</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>-27.61904761904762</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -471,7 +471,7 @@
         <v>-25.25773195876289</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         <v>-21.35306553911205</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -525,7 +525,7 @@
         <v>-24.0625</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -552,13 +552,13 @@
         <v>-22.30769230769231</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cordillera</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -567,25 +567,25 @@
         </is>
       </c>
       <c r="C8">
-        <v>3.91</v>
+        <v>3.81</v>
       </c>
       <c r="D8">
         <v>4.86</v>
       </c>
       <c r="E8">
-        <v>-0.9500000000000002</v>
+        <v>-1.05</v>
       </c>
       <c r="F8">
-        <v>-19.54732510288066</v>
+        <v>-21.60493827160494</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cordillera</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -597,22 +597,22 @@
         <v>2.58</v>
       </c>
       <c r="D9">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="E9">
-        <v>-0.7999999999999998</v>
+        <v>-0.8700000000000001</v>
       </c>
       <c r="F9">
-        <v>-23.66863905325444</v>
+        <v>-25.21739130434782</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cordillera</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -621,25 +621,25 @@
         </is>
       </c>
       <c r="C10">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="D10">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="E10">
-        <v>-0.8600000000000003</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F10">
-        <v>-21.33995037220844</v>
+        <v>-23.03921568627451</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Maipo</t>
+          <t>Cordillera</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="C11">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="D11">
-        <v>5.28</v>
+        <v>4.86</v>
       </c>
       <c r="E11">
-        <v>-1.180000000000001</v>
+        <v>-0.9500000000000002</v>
       </c>
       <c r="F11">
-        <v>-22.34848484848486</v>
+        <v>-19.54732510288066</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Maipo</t>
+          <t>Cordillera</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -675,25 +675,25 @@
         </is>
       </c>
       <c r="C12">
-        <v>3.22</v>
+        <v>2.58</v>
       </c>
       <c r="D12">
-        <v>4.38</v>
+        <v>3.38</v>
       </c>
       <c r="E12">
-        <v>-1.16</v>
+        <v>-0.7999999999999998</v>
       </c>
       <c r="F12">
-        <v>-26.48401826484018</v>
+        <v>-23.66863905325444</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maipo</t>
+          <t>Cordillera</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -702,25 +702,25 @@
         </is>
       </c>
       <c r="C13">
-        <v>3.59</v>
+        <v>3.17</v>
       </c>
       <c r="D13">
-        <v>4.76</v>
+        <v>4.03</v>
       </c>
       <c r="E13">
-        <v>-1.17</v>
+        <v>-0.8600000000000003</v>
       </c>
       <c r="F13">
-        <v>-24.57983193277311</v>
+        <v>-21.33995037220844</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Maipo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -729,25 +729,25 @@
         </is>
       </c>
       <c r="C14">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="D14">
-        <v>5.59</v>
+        <v>5.28</v>
       </c>
       <c r="E14">
-        <v>-1.37</v>
+        <v>-1.180000000000001</v>
       </c>
       <c r="F14">
-        <v>-24.50805008944544</v>
+        <v>-22.34848484848486</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Maipo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -756,25 +756,25 @@
         </is>
       </c>
       <c r="C15">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="D15">
-        <v>4.6</v>
+        <v>4.38</v>
       </c>
       <c r="E15">
-        <v>-1.34</v>
+        <v>-1.16</v>
       </c>
       <c r="F15">
-        <v>-29.1304347826087</v>
+        <v>-26.48401826484018</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Maipo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="C16">
-        <v>3.66</v>
+        <v>3.59</v>
       </c>
       <c r="D16">
-        <v>5.01</v>
+        <v>4.76</v>
       </c>
       <c r="E16">
-        <v>-1.35</v>
+        <v>-1.17</v>
       </c>
       <c r="F16">
-        <v>-26.94610778443113</v>
+        <v>-24.57983193277311</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -810,25 +810,25 @@
         </is>
       </c>
       <c r="C17">
-        <v>5.25</v>
+        <v>4.22</v>
       </c>
       <c r="D17">
-        <v>7.01</v>
+        <v>5.59</v>
       </c>
       <c r="E17">
-        <v>-1.76</v>
+        <v>-1.37</v>
       </c>
       <c r="F17">
-        <v>-25.10699001426533</v>
+        <v>-24.50805008944544</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -837,45 +837,126 @@
         </is>
       </c>
       <c r="C18">
-        <v>4.59</v>
+        <v>3.26</v>
       </c>
       <c r="D18">
-        <v>6.67</v>
+        <v>4.6</v>
       </c>
       <c r="E18">
-        <v>-2.08</v>
+        <v>-1.34</v>
       </c>
       <c r="F18">
-        <v>-31.18440779610195</v>
+        <v>-29.1304347826087</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>3.66</v>
+      </c>
+      <c r="D19">
+        <v>5.01</v>
+      </c>
+      <c r="E19">
+        <v>-1.35</v>
+      </c>
+      <c r="F19">
+        <v>-26.94610778443113</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Melipilla</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>5.25</v>
+      </c>
+      <c r="D20">
+        <v>7.01</v>
+      </c>
+      <c r="E20">
+        <v>-1.76</v>
+      </c>
+      <c r="F20">
+        <v>-25.10699001426533</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>4.59</v>
+      </c>
+      <c r="D21">
+        <v>6.67</v>
+      </c>
+      <c r="E21">
+        <v>-2.08</v>
+      </c>
+      <c r="F21">
+        <v>-31.18440779610195</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C19">
+      <c r="C22">
         <v>4.86</v>
       </c>
-      <c r="D19">
+      <c r="D22">
         <v>6.81</v>
       </c>
-      <c r="E19">
+      <c r="E22">
         <v>-1.949999999999999</v>
       </c>
-      <c r="F19">
+      <c r="F22">
         <v>-28.63436123348017</v>
       </c>
-      <c r="G19">
+      <c r="G22">
         <v>1</v>
       </c>
     </row>
@@ -968,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1317,6 +1398,60 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>4.08</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>3.14</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>3.83</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:21</t>
+    <t xml:space="preserve">2026-08-19 14:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -92,13 +92,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_peringrmin_a_2023_metropolitana.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Metropolitana</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -1049,23 +1055,23 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1088,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -1161,10 +1167,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -1172,7 +1178,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>3.88</v>
@@ -1183,7 +1189,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>2.9</v>
@@ -1194,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>3.56</v>
@@ -1205,7 +1211,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>4.03</v>
@@ -1216,7 +1222,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>3.17</v>
@@ -1227,7 +1233,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>3.82</v>
@@ -1238,7 +1244,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>4.76</v>
@@ -1249,7 +1255,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>3.59</v>
@@ -1260,7 +1266,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>4.37</v>
@@ -1271,7 +1277,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>6.81</v>
@@ -1282,7 +1288,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>4.86</v>
@@ -1293,7 +1299,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>6.04</v>
@@ -1304,7 +1310,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>3.9</v>
@@ -1315,7 +1321,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>3.03</v>
@@ -1326,7 +1332,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>3.69</v>
@@ -1337,7 +1343,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>5.01</v>
@@ -1348,7 +1354,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>3.66</v>
@@ -1359,7 +1365,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>4.53</v>
@@ -1370,7 +1376,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>4.08</v>
@@ -1381,7 +1387,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>3.14</v>
@@ -1392,7 +1398,7 @@
         <v>12</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>3.83</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:28</t>
+    <t xml:space="preserve">2026-09-07 11:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
